--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$112</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$122</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$104</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -4107,7 +4107,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 13.1, "op_wape_pct": 20.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 32075.61, "rev_act": 38803.5, "op_pred": 1931.83, "op_act": 1370.59}, {"q": "2025Q4", "rev_pred": 43350.38, "rev_act": 48599.31, "op_pred": 2610.89, "op_act": 2120.72}, {"q": "2026Q1", "rev_pred": 35410.21, "rev_act": 42611.3, "op_pred": 2132.67, "op_act": 2335.14}, {"q": "2026Q2", "rev_pred": 43160.41, "rev_act": 47248.08, "op_pred": 2599.44, "op_act": 3142.6}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 13.1, "op_wape_pct": 20.0, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 32075.61, "rev_act": 38803.5, "op_pred": 1931.83, "op_act": 1370.59}, {"q": "2025Q4", "rev_pred": 43350.38, "rev_act": 48599.31, "op_pred": 2610.89, "op_act": 2120.72}, {"q": "2026Q1", "rev_pred": 35410.21, "rev_act": 42611.3, "op_pred": 2132.67, "op_act": 2335.14}, {"q": "2026Q2", "rev_pred": 43160.41, "rev_act": 47248.08, "op_pred": 2599.44, "op_act": 3142.6}]}</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO112"/>
+  <dimension ref="A1:AO122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18305,78 +18305,47 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>691487.4</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="G89" s="18" t="n">
-        <v>-269827.27</v>
-      </c>
-      <c r="H89" s="18" t="n">
-        <v>319975.05</v>
-      </c>
-      <c r="I89" s="18" t="n">
-        <v>505198.46</v>
-      </c>
-      <c r="J89" s="18" t="n">
-        <v>69731.48</v>
-      </c>
-      <c r="K89" s="35" t="n">
-        <v>625077.72</v>
-      </c>
-      <c r="L89" s="18" t="n">
-        <v>233046.24</v>
-      </c>
-      <c r="M89" s="18" t="n">
-        <v>1025689.69</v>
-      </c>
-      <c r="N89" s="18" t="n">
-        <v>153622.84</v>
-      </c>
-      <c r="O89" s="18" t="n">
-        <v>658274.52</v>
-      </c>
-      <c r="P89" s="35" t="n">
-        <v>2070633.29</v>
-      </c>
+      <c r="K89" s="9" t="n"/>
+      <c r="P89" s="9" t="n"/>
       <c r="Q89" s="18" t="n">
-        <v>344383.65</v>
+        <v>26415</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>-477065.35</v>
+        <v>29655</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>-815354.02</v>
+        <v>25366</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>1190239.72</v>
+        <v>27766</v>
       </c>
       <c r="U89" s="35" t="n">
-        <v>242204</v>
+        <v>109202</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>-572034</v>
+        <v>20212</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>-12808</v>
+        <v>21739</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>-60085</v>
+        <v>20075</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>1396728</v>
+        <v>24720</v>
       </c>
       <c r="Z89" s="35" t="n">
-        <v>751801</v>
+        <v>86746</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>-565522</v>
+        <v>18062</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>-321130</v>
+        <v>22427</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -18398,78 +18367,47 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>5643.21</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F90" s="9" t="n"/>
-      <c r="G90" s="18" t="n">
-        <v>2457</v>
-      </c>
-      <c r="H90" s="18" t="n">
-        <v>3476.25</v>
-      </c>
-      <c r="I90" s="18" t="n">
-        <v>4392.67</v>
-      </c>
-      <c r="J90" s="18" t="n">
-        <v>7686.58</v>
-      </c>
-      <c r="K90" s="35" t="n">
-        <v>18012.5</v>
-      </c>
-      <c r="L90" s="18" t="n">
-        <v>7085.48</v>
-      </c>
-      <c r="M90" s="18" t="n">
-        <v>7617.81</v>
-      </c>
-      <c r="N90" s="18" t="n">
-        <v>19064.14</v>
-      </c>
-      <c r="O90" s="18" t="n">
-        <v>20440.44</v>
-      </c>
-      <c r="P90" s="35" t="n">
-        <v>54207.87</v>
-      </c>
+      <c r="K90" s="9" t="n"/>
+      <c r="P90" s="9" t="n"/>
       <c r="Q90" s="18" t="n">
-        <v>26476.45</v>
+        <v>240</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>28410.11</v>
+        <v>743</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>15668.88</v>
+        <v>8</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>20106.56</v>
+        <v>1418</v>
       </c>
       <c r="U90" s="35" t="n">
-        <v>90662</v>
+        <v>2409</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>17413</v>
+        <v>698</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>20101</v>
+        <v>541</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>27264</v>
+        <v>26</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>23078</v>
+        <v>2325</v>
       </c>
       <c r="Z90" s="35" t="n">
-        <v>87856</v>
+        <v>3590</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>15388</v>
+        <v>1756</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>16171</v>
+        <v>873</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -18491,70 +18429,47 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>-90503.5</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F91" s="9" t="n"/>
-      <c r="G91" s="18" t="n">
-        <v>-63465.11</v>
-      </c>
-      <c r="H91" s="18" t="n">
-        <v>-71102.49000000001</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>-63050.56</v>
-      </c>
-      <c r="J91" s="18" t="n">
-        <v>-82119.42999999999</v>
-      </c>
-      <c r="K91" s="35" t="n">
-        <v>-279737.59</v>
-      </c>
-      <c r="L91" s="18" t="n">
-        <v>-84161.85000000001</v>
-      </c>
-      <c r="M91" s="18" t="n">
-        <v>-88532.25</v>
-      </c>
+      <c r="K91" s="9" t="n"/>
       <c r="P91" s="9" t="n"/>
       <c r="Q91" s="18" t="n">
-        <v>-90670.69</v>
+        <v>78944</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>-92267.66</v>
+        <v>80594</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>-95945.89999999999</v>
+        <v>79432</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>-104145.75</v>
+        <v>90107</v>
       </c>
       <c r="U91" s="35" t="n">
-        <v>-383030</v>
+        <v>329077</v>
       </c>
       <c r="V91" s="18" t="n">
-        <v>-104168</v>
+        <v>79983</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>-82034</v>
+        <v>78493</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>-98004</v>
+        <v>84636</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>-88103</v>
+        <v>82836</v>
       </c>
       <c r="Z91" s="35" t="n">
-        <v>-372309</v>
+        <v>325948</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>-81236</v>
+        <v>76908</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>-88413</v>
+        <v>90073</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -18576,78 +18491,47 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>0</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="18" t="n">
-        <v>78</v>
-      </c>
-      <c r="H92" s="18" t="n">
-        <v>3691.69</v>
-      </c>
-      <c r="I92" s="18" t="n">
-        <v>567.53</v>
-      </c>
-      <c r="J92" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="35" t="n">
-        <v>4337.22</v>
-      </c>
-      <c r="L92" s="18" t="n">
-        <v>2014.59</v>
-      </c>
-      <c r="M92" s="18" t="n">
-        <v>2253.2</v>
-      </c>
-      <c r="N92" s="18" t="n">
-        <v>1791.4</v>
-      </c>
-      <c r="O92" s="18" t="n">
-        <v>64.13</v>
-      </c>
-      <c r="P92" s="35" t="n">
-        <v>6123.32</v>
-      </c>
+      <c r="K92" s="9" t="n"/>
+      <c r="P92" s="9" t="n"/>
       <c r="Q92" s="18" t="n">
-        <v>2089.81</v>
+        <v>52180</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>1131.69</v>
+        <v>77851</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>395.76</v>
+        <v>45633</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>388.74</v>
+        <v>84902</v>
       </c>
       <c r="U92" s="35" t="n">
-        <v>4006</v>
+        <v>260566</v>
       </c>
       <c r="V92" s="18" t="n">
-        <v>850</v>
+        <v>44941</v>
       </c>
       <c r="W92" s="18" t="n">
-        <v>562</v>
+        <v>65166</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>998</v>
+        <v>111280</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>101</v>
+        <v>60040</v>
       </c>
       <c r="Z92" s="35" t="n">
-        <v>2511</v>
+        <v>281427</v>
       </c>
       <c r="AA92" s="18" t="n">
-        <v>1280</v>
+        <v>53166</v>
       </c>
       <c r="AB92" s="19" t="n">
-        <v>217</v>
+        <v>69639</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -18669,78 +18553,47 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>-33710.82</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F93" s="9" t="n"/>
-      <c r="G93" s="18" t="n">
-        <v>-16652.38</v>
-      </c>
-      <c r="H93" s="18" t="n">
-        <v>-91112.60000000001</v>
-      </c>
-      <c r="I93" s="18" t="n">
-        <v>-84340.59</v>
-      </c>
-      <c r="J93" s="18" t="n">
-        <v>-107600.73</v>
-      </c>
-      <c r="K93" s="35" t="n">
-        <v>-299706.3</v>
-      </c>
-      <c r="L93" s="18" t="n">
-        <v>-43821.27</v>
-      </c>
-      <c r="M93" s="18" t="n">
-        <v>-144560.16</v>
-      </c>
-      <c r="N93" s="18" t="n">
-        <v>-64151.35</v>
-      </c>
-      <c r="O93" s="18" t="n">
-        <v>-96545.42</v>
-      </c>
-      <c r="P93" s="35" t="n">
-        <v>-349078.2</v>
-      </c>
+      <c r="K93" s="9" t="n"/>
+      <c r="P93" s="9" t="n"/>
       <c r="Q93" s="18" t="n">
-        <v>-18834.99</v>
+        <v>47524</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>-191470.92</v>
+        <v>66911</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>-85138.63</v>
+        <v>44516</v>
       </c>
       <c r="T93" s="18" t="n">
-        <v>-21511.46</v>
+        <v>100599</v>
       </c>
       <c r="U93" s="35" t="n">
-        <v>-316956</v>
+        <v>259550</v>
       </c>
       <c r="V93" s="18" t="n">
-        <v>-53768</v>
+        <v>44772</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>-143996</v>
+        <v>111132</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>603</v>
+        <v>81370</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>-16917</v>
+        <v>63078</v>
       </c>
       <c r="Z93" s="35" t="n">
-        <v>-214078</v>
+        <v>300352</v>
       </c>
       <c r="AA93" s="18" t="n">
-        <v>-33742</v>
+        <v>113198</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>-101241</v>
+        <v>2422</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -18762,78 +18615,47 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E94" s="18" t="n">
-        <v>157755.36</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="G94" s="18" t="n">
-        <v>185500.96</v>
-      </c>
-      <c r="H94" s="18" t="n">
-        <v>-127940.49</v>
-      </c>
-      <c r="I94" s="18" t="n">
-        <v>-46961.04</v>
-      </c>
-      <c r="J94" s="18" t="n">
-        <v>-81729.98</v>
-      </c>
-      <c r="K94" s="35" t="n">
-        <v>-71130.55</v>
-      </c>
-      <c r="L94" s="18" t="n">
-        <v>-249734.64</v>
-      </c>
-      <c r="M94" s="18" t="n">
-        <v>-109699.58</v>
-      </c>
-      <c r="N94" s="18" t="n">
-        <v>-217970.98</v>
-      </c>
-      <c r="O94" s="18" t="n">
-        <v>-239223.27</v>
-      </c>
-      <c r="P94" s="35" t="n">
-        <v>-816628.47</v>
-      </c>
+      <c r="K94" s="9" t="n"/>
+      <c r="P94" s="9" t="n"/>
       <c r="Q94" s="18" t="n">
-        <v>-154250.07</v>
+        <v>93975</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>-186315.7</v>
+        <v>52019</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>-125953.82</v>
+        <v>-57284</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>-354879.41</v>
+        <v>239243</v>
       </c>
       <c r="U94" s="35" t="n">
-        <v>-821399</v>
+        <v>327953</v>
       </c>
       <c r="V94" s="18" t="n">
-        <v>-150166</v>
+        <v>79447</v>
       </c>
       <c r="W94" s="18" t="n">
-        <v>-106593</v>
+        <v>118348</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>-205398</v>
+        <v>-71306</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>151586</v>
+        <v>5144</v>
       </c>
       <c r="Z94" s="35" t="n">
-        <v>-310571</v>
+        <v>131633</v>
       </c>
       <c r="AA94" s="18" t="n">
-        <v>-170805</v>
+        <v>146237</v>
       </c>
       <c r="AB94" s="19" t="n">
-        <v>-349054</v>
+        <v>40330</v>
       </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
@@ -18855,68 +18677,47 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E95" s="18" t="n">
-        <v>13564.32</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F95" s="9" t="n"/>
-      <c r="G95" s="18" t="n">
-        <v>3311.65</v>
-      </c>
-      <c r="H95" s="18" t="n">
-        <v>22505.98</v>
-      </c>
-      <c r="J95" s="18" t="n">
-        <v>5274.6</v>
-      </c>
       <c r="K95" s="9" t="n"/>
-      <c r="L95" s="18" t="n">
-        <v>411.03</v>
-      </c>
-      <c r="M95" s="18" t="n">
-        <v>4545</v>
-      </c>
-      <c r="N95" s="18" t="n">
-        <v>666.09</v>
-      </c>
-      <c r="O95" s="18" t="n">
-        <v>3260.74</v>
-      </c>
-      <c r="P95" s="35" t="n">
-        <v>8882.860000000001</v>
-      </c>
+      <c r="P95" s="9" t="n"/>
       <c r="Q95" s="18" t="n">
-        <v>1098.56</v>
+        <v>75245</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>4367.51</v>
+        <v>52952</v>
       </c>
       <c r="S95" s="18" t="n">
-        <v>1173.65</v>
+        <v>-49871</v>
       </c>
       <c r="T95" s="18" t="n">
-        <v>2714.28</v>
+        <v>193313</v>
       </c>
       <c r="U95" s="35" t="n">
-        <v>9354</v>
+        <v>271639</v>
       </c>
       <c r="V95" s="18" t="n">
-        <v>4383</v>
+        <v>88297</v>
+      </c>
+      <c r="W95" s="18" t="n">
+        <v>82989</v>
       </c>
       <c r="X95" s="18" t="n">
-        <v>1769</v>
+        <v>20103</v>
       </c>
       <c r="Y95" s="18" t="n">
-        <v>3253</v>
-      </c>
-      <c r="Z95" s="9" t="n"/>
+        <v>9913</v>
+      </c>
+      <c r="Z95" s="35" t="n">
+        <v>201302</v>
+      </c>
       <c r="AA95" s="18" t="n">
-        <v>1310</v>
+        <v>127914</v>
       </c>
       <c r="AB95" s="19" t="n">
-        <v>1022</v>
+        <v>16407</v>
       </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -18938,46 +18739,47 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
-        </is>
-      </c>
-      <c r="E96" s="18" t="n">
-        <v>80</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F96" s="9" t="n"/>
-      <c r="J96" s="18" t="n">
-        <v>73.38</v>
-      </c>
       <c r="K96" s="9" t="n"/>
-      <c r="N96" s="18" t="n">
-        <v>1681.81</v>
-      </c>
-      <c r="O96" s="18" t="n">
-        <v>26.57</v>
-      </c>
       <c r="P96" s="9" t="n"/>
+      <c r="Q96" s="18" t="n">
+        <v>77950</v>
+      </c>
+      <c r="R96" s="18" t="n">
+        <v>53120</v>
+      </c>
       <c r="S96" s="18" t="n">
-        <v>0</v>
+        <v>11685</v>
       </c>
       <c r="T96" s="18" t="n">
-        <v>1399</v>
-      </c>
-      <c r="U96" s="9" t="n"/>
+        <v>78182</v>
+      </c>
+      <c r="U96" s="35" t="n">
+        <v>220937</v>
+      </c>
       <c r="V96" s="18" t="n">
-        <v>302</v>
+        <v>108613</v>
       </c>
       <c r="W96" s="18" t="n">
-        <v>1090</v>
+        <v>184185</v>
+      </c>
+      <c r="X96" s="18" t="n">
+        <v>-87178</v>
       </c>
       <c r="Y96" s="18" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z96" s="9" t="n"/>
+        <v>74566</v>
+      </c>
+      <c r="Z96" s="35" t="n">
+        <v>280186</v>
+      </c>
       <c r="AA96" s="18" t="n">
-        <v>60</v>
+        <v>73472</v>
       </c>
       <c r="AB96" s="19" t="n">
-        <v>435</v>
+        <v>50788</v>
       </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -18999,78 +18801,47 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E97" s="18" t="n">
-        <v>111852.59</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F97" s="9" t="n"/>
-      <c r="G97" s="18" t="n">
-        <v>64044.24</v>
-      </c>
-      <c r="H97" s="18" t="n">
-        <v>75168.59</v>
-      </c>
-      <c r="I97" s="18" t="n">
-        <v>82299.78</v>
-      </c>
-      <c r="J97" s="18" t="n">
-        <v>127191.49</v>
-      </c>
-      <c r="K97" s="35" t="n">
-        <v>348704.1</v>
-      </c>
-      <c r="L97" s="18" t="n">
-        <v>84735.36</v>
-      </c>
-      <c r="M97" s="18" t="n">
-        <v>87812.61</v>
-      </c>
-      <c r="N97" s="18" t="n">
-        <v>96794.49000000001</v>
-      </c>
-      <c r="O97" s="18" t="n">
-        <v>126253.6</v>
-      </c>
-      <c r="P97" s="35" t="n">
-        <v>395596.06</v>
-      </c>
+      <c r="K97" s="9" t="n"/>
+      <c r="P97" s="9" t="n"/>
       <c r="Q97" s="18" t="n">
-        <v>87641.41</v>
+        <v>141624</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>112202.88</v>
+        <v>93354</v>
       </c>
       <c r="S97" s="18" t="n">
-        <v>125837.54</v>
+        <v>-81409</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>135815.17</v>
+        <v>236306</v>
       </c>
       <c r="U97" s="35" t="n">
-        <v>461497</v>
+        <v>389875</v>
       </c>
       <c r="V97" s="18" t="n">
-        <v>89838</v>
+        <v>123829</v>
       </c>
       <c r="W97" s="18" t="n">
-        <v>55944</v>
+        <v>32885</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>140259</v>
+        <v>40792</v>
       </c>
       <c r="Y97" s="18" t="n">
-        <v>117054</v>
+        <v>103249</v>
       </c>
       <c r="Z97" s="35" t="n">
-        <v>403095</v>
+        <v>300755</v>
       </c>
       <c r="AA97" s="18" t="n">
-        <v>115089</v>
+        <v>288806</v>
       </c>
       <c r="AB97" s="19" t="n">
-        <v>48651</v>
+        <v>204374</v>
       </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
@@ -19092,78 +18863,47 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E98" s="18" t="n">
-        <v>183048.87</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F98" s="9" t="n"/>
-      <c r="G98" s="18" t="n">
-        <v>108015.16</v>
-      </c>
-      <c r="H98" s="18" t="n">
-        <v>123777.78</v>
-      </c>
-      <c r="I98" s="18" t="n">
-        <v>128281.83</v>
-      </c>
-      <c r="J98" s="18" t="n">
-        <v>184636.06</v>
-      </c>
-      <c r="K98" s="35" t="n">
-        <v>544710.83</v>
-      </c>
-      <c r="L98" s="18" t="n">
-        <v>125145.94</v>
-      </c>
-      <c r="M98" s="18" t="n">
-        <v>134067.78</v>
-      </c>
-      <c r="N98" s="18" t="n">
-        <v>159386.51</v>
-      </c>
-      <c r="O98" s="18" t="n">
-        <v>184593.07</v>
-      </c>
-      <c r="P98" s="35" t="n">
-        <v>603193.3</v>
-      </c>
+      <c r="K98" s="9" t="n"/>
+      <c r="P98" s="9" t="n"/>
       <c r="Q98" s="18" t="n">
-        <v>128617.21</v>
+        <v>-52529</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>161364.35</v>
+        <v>-50939</v>
       </c>
       <c r="S98" s="18" t="n">
-        <v>159774.86</v>
+        <v>-54066</v>
       </c>
       <c r="T98" s="18" t="n">
-        <v>203891.58</v>
+        <v>-62341</v>
       </c>
       <c r="U98" s="35" t="n">
-        <v>653648</v>
+        <v>-219875</v>
       </c>
       <c r="V98" s="18" t="n">
-        <v>131389</v>
+        <v>-59771</v>
       </c>
       <c r="W98" s="18" t="n">
-        <v>142734</v>
+        <v>-56754</v>
       </c>
       <c r="X98" s="18" t="n">
-        <v>233332</v>
+        <v>-64561</v>
       </c>
       <c r="Y98" s="18" t="n">
-        <v>190656</v>
+        <v>-58116</v>
       </c>
       <c r="Z98" s="35" t="n">
-        <v>698111</v>
+        <v>-239202</v>
       </c>
       <c r="AA98" s="18" t="n">
-        <v>171431</v>
+        <v>-58846</v>
       </c>
       <c r="AB98" s="19" t="n">
-        <v>103829</v>
+        <v>-67646</v>
       </c>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
@@ -19185,78 +18925,78 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E99" s="18" t="n">
-        <v>71196.28</v>
+        <v>691487.4</v>
       </c>
       <c r="F99" s="9" t="n"/>
       <c r="G99" s="18" t="n">
-        <v>43970.92</v>
+        <v>-269827.27</v>
       </c>
       <c r="H99" s="18" t="n">
-        <v>48609.19</v>
+        <v>319975.05</v>
       </c>
       <c r="I99" s="18" t="n">
-        <v>45982.05</v>
+        <v>505198.46</v>
       </c>
       <c r="J99" s="18" t="n">
-        <v>57444.57</v>
+        <v>69731.48</v>
       </c>
       <c r="K99" s="35" t="n">
-        <v>196006.73</v>
+        <v>625077.72</v>
       </c>
       <c r="L99" s="18" t="n">
-        <v>40410.58</v>
+        <v>233046.24</v>
       </c>
       <c r="M99" s="18" t="n">
-        <v>46255.17</v>
+        <v>1025689.69</v>
       </c>
       <c r="N99" s="18" t="n">
-        <v>62592.02</v>
+        <v>153622.84</v>
       </c>
       <c r="O99" s="18" t="n">
-        <v>58339.47</v>
+        <v>658274.52</v>
       </c>
       <c r="P99" s="35" t="n">
-        <v>207597.24</v>
+        <v>2070633.29</v>
       </c>
       <c r="Q99" s="18" t="n">
-        <v>40975.8</v>
+        <v>344383.65</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>49161.47</v>
+        <v>-477065.35</v>
       </c>
       <c r="S99" s="18" t="n">
-        <v>33937.32</v>
+        <v>-815354.02</v>
       </c>
       <c r="T99" s="18" t="n">
-        <v>68076.41</v>
+        <v>1190239.72</v>
       </c>
       <c r="U99" s="35" t="n">
-        <v>192151</v>
+        <v>242204</v>
       </c>
       <c r="V99" s="18" t="n">
-        <v>41551</v>
+        <v>-572034</v>
       </c>
       <c r="W99" s="18" t="n">
-        <v>86790</v>
+        <v>-12808</v>
       </c>
       <c r="X99" s="18" t="n">
-        <v>93073</v>
+        <v>-60085</v>
       </c>
       <c r="Y99" s="18" t="n">
-        <v>73602</v>
+        <v>1396728</v>
       </c>
       <c r="Z99" s="35" t="n">
-        <v>295016</v>
+        <v>751801</v>
       </c>
       <c r="AA99" s="18" t="n">
-        <v>56342</v>
+        <v>-565522</v>
       </c>
       <c r="AB99" s="19" t="n">
-        <v>55178</v>
+        <v>-321130</v>
       </c>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
@@ -19278,78 +19018,78 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E100" s="18" t="n">
-        <v>-725298.89</v>
+        <v>5643.21</v>
       </c>
       <c r="F100" s="9" t="n"/>
       <c r="G100" s="18" t="n">
-        <v>-261633.54</v>
+        <v>2457</v>
       </c>
       <c r="H100" s="18" t="n">
-        <v>-700634.45</v>
+        <v>3476.25</v>
       </c>
       <c r="I100" s="18" t="n">
-        <v>-228278.38</v>
+        <v>4392.67</v>
       </c>
       <c r="J100" s="18" t="n">
-        <v>58093.74</v>
+        <v>7686.58</v>
       </c>
       <c r="K100" s="35" t="n">
-        <v>-1132452.63</v>
+        <v>18012.5</v>
       </c>
       <c r="L100" s="18" t="n">
-        <v>165390.92</v>
+        <v>7085.48</v>
       </c>
       <c r="M100" s="18" t="n">
-        <v>200327.56</v>
+        <v>7617.81</v>
       </c>
       <c r="N100" s="18" t="n">
-        <v>-410177.67</v>
+        <v>19064.14</v>
       </c>
       <c r="O100" s="18" t="n">
-        <v>-8477.290000000001</v>
+        <v>20440.44</v>
       </c>
       <c r="P100" s="35" t="n">
-        <v>-52936.48</v>
+        <v>54207.87</v>
       </c>
       <c r="Q100" s="18" t="n">
-        <v>38177.47</v>
+        <v>26476.45</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>278842.46</v>
+        <v>28410.11</v>
       </c>
       <c r="S100" s="18" t="n">
-        <v>718708.26</v>
+        <v>15668.88</v>
       </c>
       <c r="T100" s="18" t="n">
-        <v>-427306.19</v>
+        <v>20106.56</v>
       </c>
       <c r="U100" s="35" t="n">
-        <v>608422</v>
+        <v>90662</v>
       </c>
       <c r="V100" s="18" t="n">
-        <v>420526</v>
+        <v>17413</v>
       </c>
       <c r="W100" s="18" t="n">
-        <v>-107658</v>
+        <v>20101</v>
       </c>
       <c r="X100" s="18" t="n">
-        <v>401926</v>
+        <v>27264</v>
       </c>
       <c r="Y100" s="18" t="n">
-        <v>-1002739</v>
+        <v>23078</v>
       </c>
       <c r="Z100" s="35" t="n">
-        <v>-287945</v>
+        <v>87856</v>
       </c>
       <c r="AA100" s="18" t="n">
-        <v>666065</v>
+        <v>15388</v>
       </c>
       <c r="AB100" s="19" t="n">
-        <v>76716</v>
+        <v>16171</v>
       </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
@@ -19371,78 +19111,70 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>사채의증가</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E101" s="18" t="n">
-        <v>14988.7</v>
+        <v>-90503.5</v>
       </c>
       <c r="F101" s="9" t="n"/>
       <c r="G101" s="18" t="n">
-        <v>110000</v>
+        <v>-63465.11</v>
       </c>
       <c r="H101" s="18" t="n">
-        <v>80000</v>
+        <v>-71102.49000000001</v>
       </c>
       <c r="I101" s="18" t="n">
-        <v>149740.03</v>
+        <v>-63050.56</v>
       </c>
       <c r="J101" s="18" t="n">
-        <v>27417.07</v>
+        <v>-82119.42999999999</v>
       </c>
       <c r="K101" s="35" t="n">
-        <v>367157.1</v>
+        <v>-279737.59</v>
       </c>
       <c r="L101" s="18" t="n">
-        <v>57000</v>
+        <v>-84161.85000000001</v>
       </c>
       <c r="M101" s="18" t="n">
-        <v>79671.25999999999</v>
-      </c>
-      <c r="N101" s="18" t="n">
-        <v>372527</v>
-      </c>
-      <c r="O101" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="35" t="n">
-        <v>509198.26</v>
-      </c>
+        <v>-88532.25</v>
+      </c>
+      <c r="P101" s="9" t="n"/>
       <c r="Q101" s="18" t="n">
-        <v>177240.29</v>
+        <v>-90670.69</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>66844.99000000001</v>
+        <v>-92267.66</v>
       </c>
       <c r="S101" s="18" t="n">
-        <v>229285.71</v>
+        <v>-95945.89999999999</v>
       </c>
       <c r="T101" s="18" t="n">
-        <v>551.01</v>
+        <v>-104145.75</v>
       </c>
       <c r="U101" s="35" t="n">
-        <v>473922</v>
+        <v>-383030</v>
       </c>
       <c r="V101" s="18" t="n">
-        <v>55736</v>
+        <v>-104168</v>
       </c>
       <c r="W101" s="18" t="n">
-        <v>128006</v>
+        <v>-82034</v>
       </c>
       <c r="X101" s="18" t="n">
-        <v>61729</v>
+        <v>-98004</v>
       </c>
       <c r="Y101" s="18" t="n">
-        <v>40763</v>
+        <v>-88103</v>
       </c>
       <c r="Z101" s="35" t="n">
-        <v>286234</v>
+        <v>-372309</v>
       </c>
       <c r="AA101" s="18" t="n">
-        <v>9980</v>
+        <v>-81236</v>
       </c>
       <c r="AB101" s="19" t="n">
-        <v>9982</v>
+        <v>-88413</v>
       </c>
       <c r="AC101" s="10" t="n"/>
       <c r="AD101" s="10" t="n"/>
@@ -19464,70 +19196,78 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E102" s="18" t="n">
-        <v>359225.3</v>
+        <v>0</v>
       </c>
       <c r="F102" s="9" t="n"/>
       <c r="G102" s="18" t="n">
-        <v>500000</v>
+        <v>78</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>1409482.17</v>
+        <v>3691.69</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>37025.79</v>
+        <v>567.53</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>619867.6899999999</v>
+        <v>0</v>
       </c>
       <c r="K102" s="35" t="n">
-        <v>2566375.65</v>
+        <v>4337.22</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>342331.24</v>
+        <v>2014.59</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>147539.3</v>
+        <v>2253.2</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>16043.05</v>
+        <v>1791.4</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>140152.34</v>
+        <v>64.13</v>
       </c>
       <c r="P102" s="35" t="n">
-        <v>646065.9300000001</v>
+        <v>6123.32</v>
       </c>
       <c r="Q102" s="18" t="n">
-        <v>570000</v>
+        <v>2089.81</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>142067.5</v>
+        <v>1131.69</v>
       </c>
       <c r="S102" s="18" t="n">
-        <v>483477.21</v>
+        <v>395.76</v>
       </c>
       <c r="T102" s="18" t="n">
-        <v>142964.29</v>
+        <v>388.74</v>
       </c>
       <c r="U102" s="35" t="n">
-        <v>1338509</v>
+        <v>4006</v>
       </c>
       <c r="V102" s="18" t="n">
-        <v>619295</v>
+        <v>850</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>562</v>
       </c>
       <c r="X102" s="18" t="n">
-        <v>70110</v>
-      </c>
-      <c r="Z102" s="9" t="n"/>
+        <v>998</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>101</v>
+      </c>
+      <c r="Z102" s="35" t="n">
+        <v>2511</v>
+      </c>
       <c r="AA102" s="18" t="n">
-        <v>160000</v>
+        <v>1280</v>
       </c>
       <c r="AB102" s="19" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="AC102" s="10" t="n"/>
       <c r="AD102" s="10" t="n"/>
@@ -19549,60 +19289,79 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E103" s="18" t="n">
-        <v>287622.79</v>
+        <v>-33710.82</v>
       </c>
       <c r="F103" s="9" t="n"/>
       <c r="G103" s="18" t="n">
-        <v>1935769.63</v>
+        <v>-16652.38</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>241855.52</v>
+        <v>-91112.60000000001</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>190635.03</v>
+        <v>-84340.59</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>28.29</v>
+        <v>-107600.73</v>
       </c>
       <c r="K103" s="35" t="n">
-        <v>2368288.47</v>
+        <v>-299706.3</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>22971.1</v>
+        <v>-43821.27</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>188658.4</v>
+        <v>-144560.16</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>17158.17</v>
+        <v>-64151.35</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>13603.23</v>
+        <v>-96545.42</v>
       </c>
       <c r="P103" s="35" t="n">
-        <v>242390.9</v>
+        <v>-349078.2</v>
       </c>
       <c r="Q103" s="18" t="n">
-        <v>0</v>
+        <v>-18834.99</v>
       </c>
       <c r="R103" s="18" t="n">
-        <v>0</v>
+        <v>-191470.92</v>
       </c>
       <c r="S103" s="18" t="n">
-        <v>0</v>
+        <v>-85138.63</v>
       </c>
       <c r="T103" s="18" t="n">
-        <v>0</v>
+        <v>-21511.46</v>
       </c>
       <c r="U103" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z103" s="9" t="n"/>
-      <c r="AB103" s="5" t="n"/>
+        <v>-316956</v>
+      </c>
+      <c r="V103" s="18" t="n">
+        <v>-53768</v>
+      </c>
+      <c r="W103" s="18" t="n">
+        <v>-143996</v>
+      </c>
+      <c r="X103" s="18" t="n">
+        <v>603</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>-16917</v>
+      </c>
+      <c r="Z103" s="35" t="n">
+        <v>-214078</v>
+      </c>
+      <c r="AA103" s="18" t="n">
+        <v>-33742</v>
+      </c>
+      <c r="AB103" s="19" t="n">
+        <v>-101241</v>
+      </c>
       <c r="AC103" s="10" t="n"/>
       <c r="AD103" s="10" t="n"/>
       <c r="AE103" s="11" t="n"/>
@@ -19623,73 +19382,78 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E104" s="18" t="n">
-        <v>836013.09</v>
+        <v>157755.36</v>
       </c>
       <c r="F104" s="9" t="n"/>
       <c r="G104" s="18" t="n">
-        <v>346221.39</v>
+        <v>185500.96</v>
       </c>
       <c r="H104" s="18" t="n">
-        <v>127131.44</v>
+        <v>-127940.49</v>
       </c>
       <c r="I104" s="18" t="n">
-        <v>12405.36</v>
+        <v>-46961.04</v>
       </c>
       <c r="J104" s="18" t="n">
-        <v>432084.47</v>
+        <v>-81729.98</v>
       </c>
       <c r="K104" s="35" t="n">
-        <v>917842.66</v>
+        <v>-71130.55</v>
       </c>
       <c r="L104" s="18" t="n">
-        <v>113550.5</v>
+        <v>-249734.64</v>
       </c>
       <c r="M104" s="18" t="n">
-        <v>15000</v>
+        <v>-109699.58</v>
       </c>
       <c r="N104" s="18" t="n">
-        <v>504877.14</v>
+        <v>-217970.98</v>
       </c>
       <c r="O104" s="18" t="n">
-        <v>102500</v>
+        <v>-239223.27</v>
       </c>
       <c r="P104" s="35" t="n">
-        <v>735927.64</v>
+        <v>-816628.47</v>
       </c>
       <c r="Q104" s="18" t="n">
-        <v>743000</v>
+        <v>-154250.07</v>
       </c>
       <c r="R104" s="18" t="n">
-        <v>117500</v>
+        <v>-186315.7</v>
       </c>
       <c r="S104" s="18" t="n">
-        <v>261063.36</v>
+        <v>-125953.82</v>
       </c>
       <c r="T104" s="18" t="n">
-        <v>427399.64</v>
+        <v>-354879.41</v>
       </c>
       <c r="U104" s="35" t="n">
-        <v>1548963</v>
+        <v>-821399</v>
       </c>
       <c r="V104" s="18" t="n">
-        <v>52900</v>
+        <v>-150166</v>
       </c>
       <c r="W104" s="18" t="n">
-        <v>177100</v>
+        <v>-106593</v>
+      </c>
+      <c r="X104" s="18" t="n">
+        <v>-205398</v>
       </c>
       <c r="Y104" s="18" t="n">
-        <v>16250</v>
-      </c>
-      <c r="Z104" s="9" t="n"/>
+        <v>151586</v>
+      </c>
+      <c r="Z104" s="35" t="n">
+        <v>-310571</v>
+      </c>
       <c r="AA104" s="18" t="n">
-        <v>153583</v>
+        <v>-170805</v>
       </c>
       <c r="AB104" s="19" t="n">
-        <v>29584</v>
+        <v>-349054</v>
       </c>
       <c r="AC104" s="10" t="n"/>
       <c r="AD104" s="10" t="n"/>
@@ -19711,78 +19475,68 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E105" s="18" t="n">
-        <v>23524.24</v>
+        <v>13564.32</v>
       </c>
       <c r="F105" s="9" t="n"/>
       <c r="G105" s="18" t="n">
-        <v>19001.42</v>
+        <v>3311.65</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>26700.82</v>
-      </c>
-      <c r="I105" s="18" t="n">
-        <v>9748.52</v>
+        <v>22505.98</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>24055.71</v>
-      </c>
-      <c r="K105" s="35" t="n">
-        <v>79506.47</v>
-      </c>
+        <v>5274.6</v>
+      </c>
+      <c r="K105" s="9" t="n"/>
       <c r="L105" s="18" t="n">
-        <v>18610.11</v>
+        <v>411.03</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>22363.11</v>
+        <v>4545</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>18010.72</v>
+        <v>666.09</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>25169.71</v>
+        <v>3260.74</v>
       </c>
       <c r="P105" s="35" t="n">
-        <v>84153.64999999999</v>
+        <v>8882.860000000001</v>
       </c>
       <c r="Q105" s="18" t="n">
-        <v>20373.78</v>
+        <v>1098.56</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>20760.88</v>
+        <v>4367.51</v>
       </c>
       <c r="S105" s="18" t="n">
-        <v>23131.57</v>
+        <v>1173.65</v>
       </c>
       <c r="T105" s="18" t="n">
-        <v>29800.77</v>
+        <v>2714.28</v>
       </c>
       <c r="U105" s="35" t="n">
-        <v>94067</v>
+        <v>9354</v>
       </c>
       <c r="V105" s="18" t="n">
-        <v>24723</v>
-      </c>
-      <c r="W105" s="18" t="n">
-        <v>26626</v>
+        <v>4383</v>
       </c>
       <c r="X105" s="18" t="n">
-        <v>27173</v>
+        <v>1769</v>
       </c>
       <c r="Y105" s="18" t="n">
-        <v>30945</v>
-      </c>
-      <c r="Z105" s="35" t="n">
-        <v>109467</v>
-      </c>
+        <v>3253</v>
+      </c>
+      <c r="Z105" s="9" t="n"/>
       <c r="AA105" s="18" t="n">
-        <v>25911</v>
+        <v>1310</v>
       </c>
       <c r="AB105" s="19" t="n">
-        <v>28465</v>
+        <v>1022</v>
       </c>
       <c r="AC105" s="10" t="n"/>
       <c r="AD105" s="10" t="n"/>
@@ -19804,18 +19558,47 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E106" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="F106" s="9" t="n"/>
+      <c r="J106" s="18" t="n">
+        <v>73.38</v>
+      </c>
+      <c r="K106" s="9" t="n"/>
+      <c r="N106" s="18" t="n">
+        <v>1681.81</v>
+      </c>
+      <c r="O106" s="18" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="P106" s="9" t="n"/>
+      <c r="S106" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F106" s="9" t="n"/>
-      <c r="K106" s="9" t="n"/>
-      <c r="P106" s="9" t="n"/>
+      <c r="T106" s="18" t="n">
+        <v>1399</v>
+      </c>
       <c r="U106" s="9" t="n"/>
+      <c r="V106" s="18" t="n">
+        <v>302</v>
+      </c>
+      <c r="W106" s="18" t="n">
+        <v>1090</v>
+      </c>
+      <c r="Y106" s="18" t="n">
+        <v>55</v>
+      </c>
       <c r="Z106" s="9" t="n"/>
-      <c r="AB106" s="5" t="n"/>
+      <c r="AA106" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB106" s="19" t="n">
+        <v>435</v>
+      </c>
       <c r="AC106" s="10" t="n"/>
       <c r="AD106" s="10" t="n"/>
       <c r="AE106" s="11" t="n"/>
@@ -19836,78 +19619,78 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E107" s="18" t="n">
-        <v>103901.2</v>
+        <v>111852.59</v>
       </c>
       <c r="F107" s="9" t="n"/>
       <c r="G107" s="18" t="n">
-        <v>-320352.95</v>
+        <v>64044.24</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>-490837.54</v>
+        <v>75168.59</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>369611.48</v>
+        <v>82299.78</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>-71187.38</v>
+        <v>127191.49</v>
       </c>
       <c r="K107" s="35" t="n">
-        <v>-512766.39</v>
+        <v>348704.1</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>196057.84</v>
+        <v>84735.36</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>1132627.03</v>
+        <v>87812.61</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>-454345.21</v>
+        <v>96794.49000000001</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>350009.73</v>
+        <v>126253.6</v>
       </c>
       <c r="P107" s="35" t="n">
-        <v>1224349.39</v>
+        <v>395596.06</v>
       </c>
       <c r="Q107" s="18" t="n">
-        <v>299912.81</v>
+        <v>87641.41</v>
       </c>
       <c r="R107" s="18" t="n">
-        <v>-334324.58</v>
+        <v>112202.88</v>
       </c>
       <c r="S107" s="18" t="n">
-        <v>-298168.3</v>
+        <v>125837.54</v>
       </c>
       <c r="T107" s="18" t="n">
-        <v>610691.0699999999</v>
+        <v>135815.17</v>
       </c>
       <c r="U107" s="35" t="n">
-        <v>278111</v>
+        <v>461497</v>
       </c>
       <c r="V107" s="18" t="n">
-        <v>-288638</v>
+        <v>89838</v>
       </c>
       <c r="W107" s="18" t="n">
-        <v>-335355</v>
+        <v>55944</v>
       </c>
       <c r="X107" s="18" t="n">
-        <v>129896</v>
+        <v>140259</v>
       </c>
       <c r="Y107" s="18" t="n">
-        <v>676796</v>
+        <v>117054</v>
       </c>
       <c r="Z107" s="35" t="n">
-        <v>182699</v>
+        <v>403095</v>
       </c>
       <c r="AA107" s="18" t="n">
-        <v>9533</v>
+        <v>115089</v>
       </c>
       <c r="AB107" s="19" t="n">
-        <v>-548642</v>
+        <v>48651</v>
       </c>
       <c r="AC107" s="10" t="n"/>
       <c r="AD107" s="10" t="n"/>
@@ -19929,78 +19712,78 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E108" s="18" t="n">
-        <v>103901.2</v>
+        <v>183048.87</v>
       </c>
       <c r="F108" s="9" t="n"/>
       <c r="G108" s="18" t="n">
-        <v>1588251.04</v>
+        <v>108015.16</v>
       </c>
       <c r="H108" s="18" t="n">
-        <v>-490837.54</v>
+        <v>123777.78</v>
       </c>
       <c r="I108" s="18" t="n">
-        <v>369611.48</v>
+        <v>128281.83</v>
       </c>
       <c r="J108" s="18" t="n">
-        <v>-71187.38</v>
+        <v>184636.06</v>
       </c>
       <c r="K108" s="35" t="n">
-        <v>1395837.6</v>
+        <v>544710.83</v>
       </c>
       <c r="L108" s="18" t="n">
-        <v>1591895.43</v>
+        <v>125145.94</v>
       </c>
       <c r="M108" s="18" t="n">
-        <v>1132627.04</v>
+        <v>134067.78</v>
       </c>
       <c r="N108" s="18" t="n">
-        <v>-454345.21</v>
+        <v>159386.51</v>
       </c>
       <c r="O108" s="18" t="n">
-        <v>350009.72</v>
+        <v>184593.07</v>
       </c>
       <c r="P108" s="35" t="n">
-        <v>2620186.98</v>
+        <v>603193.3</v>
       </c>
       <c r="Q108" s="18" t="n">
-        <v>2920099.79</v>
+        <v>128617.21</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>-334324.57</v>
+        <v>161364.35</v>
       </c>
       <c r="S108" s="18" t="n">
-        <v>-298168.31</v>
+        <v>159774.86</v>
       </c>
       <c r="T108" s="18" t="n">
-        <v>610691.09</v>
+        <v>203891.58</v>
       </c>
       <c r="U108" s="35" t="n">
-        <v>2898298</v>
+        <v>653648</v>
       </c>
       <c r="V108" s="18" t="n">
-        <v>2609660</v>
+        <v>131389</v>
       </c>
       <c r="W108" s="18" t="n">
-        <v>-335355</v>
+        <v>142734</v>
       </c>
       <c r="X108" s="18" t="n">
-        <v>129896</v>
+        <v>233332</v>
       </c>
       <c r="Y108" s="18" t="n">
-        <v>676796</v>
+        <v>190656</v>
       </c>
       <c r="Z108" s="35" t="n">
-        <v>3080997</v>
+        <v>698111</v>
       </c>
       <c r="AA108" s="18" t="n">
-        <v>3090530</v>
+        <v>171431</v>
       </c>
       <c r="AB108" s="19" t="n">
-        <v>-548642</v>
+        <v>103829</v>
       </c>
       <c r="AC108" s="10" t="n"/>
       <c r="AD108" s="10" t="n"/>
@@ -20022,70 +19805,78 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
-        </is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>71196.28</v>
       </c>
       <c r="F109" s="9" t="n"/>
       <c r="G109" s="18" t="n">
-        <v>264.4</v>
+        <v>43970.92</v>
       </c>
       <c r="H109" s="18" t="n">
-        <v>1398398.16</v>
+        <v>48609.19</v>
       </c>
       <c r="I109" s="18" t="n">
-        <v>139746.7</v>
+        <v>45982.05</v>
       </c>
       <c r="J109" s="18" t="n">
-        <v>130625.53</v>
+        <v>57444.57</v>
       </c>
       <c r="K109" s="35" t="n">
-        <v>1669034.79</v>
+        <v>196006.73</v>
       </c>
       <c r="L109" s="18" t="n">
-        <v>68903.58</v>
+        <v>40410.58</v>
       </c>
       <c r="M109" s="18" t="n">
-        <v>104109.82</v>
+        <v>46255.17</v>
       </c>
       <c r="N109" s="18" t="n">
-        <v>213919.53</v>
+        <v>62592.02</v>
       </c>
       <c r="O109" s="18" t="n">
-        <v>3878.58</v>
+        <v>58339.47</v>
       </c>
       <c r="P109" s="35" t="n">
-        <v>390811.51</v>
+        <v>207597.24</v>
       </c>
       <c r="Q109" s="18" t="n">
-        <v>169156.77</v>
+        <v>40975.8</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>3223.79</v>
+        <v>49161.47</v>
       </c>
       <c r="S109" s="18" t="n">
-        <v>202808.55</v>
+        <v>33937.32</v>
       </c>
       <c r="T109" s="18" t="n">
-        <v>90043.89</v>
+        <v>68076.41</v>
       </c>
       <c r="U109" s="35" t="n">
-        <v>465233</v>
+        <v>192151</v>
       </c>
       <c r="V109" s="18" t="n">
-        <v>397326</v>
+        <v>41551</v>
+      </c>
+      <c r="W109" s="18" t="n">
+        <v>86790</v>
       </c>
       <c r="X109" s="18" t="n">
-        <v>25737</v>
+        <v>93073</v>
       </c>
       <c r="Y109" s="18" t="n">
-        <v>382368</v>
-      </c>
-      <c r="Z109" s="9" t="n"/>
+        <v>73602</v>
+      </c>
+      <c r="Z109" s="35" t="n">
+        <v>295016</v>
+      </c>
       <c r="AA109" s="18" t="n">
-        <v>6154</v>
+        <v>56342</v>
       </c>
       <c r="AB109" s="19" t="n">
-        <v>26321</v>
+        <v>55178</v>
       </c>
       <c r="AC109" s="10" t="n"/>
       <c r="AD109" s="10" t="n"/>
@@ -20107,21 +19898,79 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>사채의감소</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="n">
+        <v>-725298.89</v>
       </c>
       <c r="F110" s="9" t="n"/>
+      <c r="G110" s="18" t="n">
+        <v>-261633.54</v>
+      </c>
+      <c r="H110" s="18" t="n">
+        <v>-700634.45</v>
+      </c>
       <c r="I110" s="18" t="n">
-        <v>11104.95</v>
+        <v>-228278.38</v>
       </c>
       <c r="J110" s="18" t="n">
-        <v>7118.17</v>
-      </c>
-      <c r="K110" s="9" t="n"/>
-      <c r="P110" s="9" t="n"/>
-      <c r="U110" s="9" t="n"/>
-      <c r="Z110" s="9" t="n"/>
-      <c r="AB110" s="5" t="n"/>
+        <v>58093.74</v>
+      </c>
+      <c r="K110" s="35" t="n">
+        <v>-1132452.63</v>
+      </c>
+      <c r="L110" s="18" t="n">
+        <v>165390.92</v>
+      </c>
+      <c r="M110" s="18" t="n">
+        <v>200327.56</v>
+      </c>
+      <c r="N110" s="18" t="n">
+        <v>-410177.67</v>
+      </c>
+      <c r="O110" s="18" t="n">
+        <v>-8477.290000000001</v>
+      </c>
+      <c r="P110" s="35" t="n">
+        <v>-52936.48</v>
+      </c>
+      <c r="Q110" s="18" t="n">
+        <v>38177.47</v>
+      </c>
+      <c r="R110" s="18" t="n">
+        <v>278842.46</v>
+      </c>
+      <c r="S110" s="18" t="n">
+        <v>718708.26</v>
+      </c>
+      <c r="T110" s="18" t="n">
+        <v>-427306.19</v>
+      </c>
+      <c r="U110" s="35" t="n">
+        <v>608422</v>
+      </c>
+      <c r="V110" s="18" t="n">
+        <v>420526</v>
+      </c>
+      <c r="W110" s="18" t="n">
+        <v>-107658</v>
+      </c>
+      <c r="X110" s="18" t="n">
+        <v>401926</v>
+      </c>
+      <c r="Y110" s="18" t="n">
+        <v>-1002739</v>
+      </c>
+      <c r="Z110" s="35" t="n">
+        <v>-287945</v>
+      </c>
+      <c r="AA110" s="18" t="n">
+        <v>666065</v>
+      </c>
+      <c r="AB110" s="19" t="n">
+        <v>76716</v>
+      </c>
       <c r="AC110" s="10" t="n"/>
       <c r="AD110" s="10" t="n"/>
       <c r="AE110" s="11" t="n"/>
@@ -20142,18 +19991,79 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>배당금지급</t>
-        </is>
+          <t>사채의증가</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="n">
+        <v>14988.7</v>
       </c>
       <c r="F111" s="9" t="n"/>
+      <c r="G111" s="18" t="n">
+        <v>110000</v>
+      </c>
+      <c r="H111" s="18" t="n">
+        <v>80000</v>
+      </c>
       <c r="I111" s="18" t="n">
-        <v>32052.63</v>
-      </c>
-      <c r="K111" s="9" t="n"/>
-      <c r="P111" s="9" t="n"/>
-      <c r="U111" s="9" t="n"/>
-      <c r="Z111" s="9" t="n"/>
-      <c r="AB111" s="5" t="n"/>
+        <v>149740.03</v>
+      </c>
+      <c r="J111" s="18" t="n">
+        <v>27417.07</v>
+      </c>
+      <c r="K111" s="35" t="n">
+        <v>367157.1</v>
+      </c>
+      <c r="L111" s="18" t="n">
+        <v>57000</v>
+      </c>
+      <c r="M111" s="18" t="n">
+        <v>79671.25999999999</v>
+      </c>
+      <c r="N111" s="18" t="n">
+        <v>372527</v>
+      </c>
+      <c r="O111" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" s="35" t="n">
+        <v>509198.26</v>
+      </c>
+      <c r="Q111" s="18" t="n">
+        <v>177240.29</v>
+      </c>
+      <c r="R111" s="18" t="n">
+        <v>66844.99000000001</v>
+      </c>
+      <c r="S111" s="18" t="n">
+        <v>229285.71</v>
+      </c>
+      <c r="T111" s="18" t="n">
+        <v>551.01</v>
+      </c>
+      <c r="U111" s="35" t="n">
+        <v>473922</v>
+      </c>
+      <c r="V111" s="18" t="n">
+        <v>55736</v>
+      </c>
+      <c r="W111" s="18" t="n">
+        <v>128006</v>
+      </c>
+      <c r="X111" s="18" t="n">
+        <v>61729</v>
+      </c>
+      <c r="Y111" s="18" t="n">
+        <v>40763</v>
+      </c>
+      <c r="Z111" s="35" t="n">
+        <v>286234</v>
+      </c>
+      <c r="AA111" s="18" t="n">
+        <v>9980</v>
+      </c>
+      <c r="AB111" s="19" t="n">
+        <v>9982</v>
+      </c>
       <c r="AC111" s="10" t="n"/>
       <c r="AD111" s="10" t="n"/>
       <c r="AE111" s="11" t="n"/>
@@ -20174,39 +20084,70 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="n">
+        <v>359225.3</v>
       </c>
       <c r="F112" s="9" t="n"/>
-      <c r="K112" s="9" t="n"/>
-      <c r="P112" s="9" t="n"/>
+      <c r="G112" s="18" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H112" s="18" t="n">
+        <v>1409482.17</v>
+      </c>
+      <c r="I112" s="18" t="n">
+        <v>37025.79</v>
+      </c>
+      <c r="J112" s="18" t="n">
+        <v>619867.6899999999</v>
+      </c>
+      <c r="K112" s="35" t="n">
+        <v>2566375.65</v>
+      </c>
+      <c r="L112" s="18" t="n">
+        <v>342331.24</v>
+      </c>
+      <c r="M112" s="18" t="n">
+        <v>147539.3</v>
+      </c>
+      <c r="N112" s="18" t="n">
+        <v>16043.05</v>
+      </c>
+      <c r="O112" s="18" t="n">
+        <v>140152.34</v>
+      </c>
+      <c r="P112" s="35" t="n">
+        <v>646065.9300000001</v>
+      </c>
       <c r="Q112" s="18" t="n">
-        <v>228125</v>
+        <v>570000</v>
       </c>
       <c r="R112" s="18" t="n">
-        <v>259807.97</v>
+        <v>142067.5</v>
       </c>
       <c r="S112" s="18" t="n">
-        <v>536197.23</v>
+        <v>483477.21</v>
       </c>
       <c r="T112" s="18" t="n">
-        <v>38738.8</v>
+        <v>142964.29</v>
       </c>
       <c r="U112" s="35" t="n">
-        <v>1062869</v>
+        <v>1338509</v>
       </c>
       <c r="V112" s="18" t="n">
-        <v>209464</v>
+        <v>619295</v>
       </c>
       <c r="X112" s="18" t="n">
-        <v>291757</v>
+        <v>70110</v>
       </c>
       <c r="Z112" s="9" t="n"/>
       <c r="AA112" s="18" t="n">
-        <v>685152</v>
+        <v>160000</v>
       </c>
       <c r="AB112" s="19" t="n">
-        <v>331908</v>
+        <v>0</v>
       </c>
       <c r="AC112" s="10" t="n"/>
       <c r="AD112" s="10" t="n"/>
@@ -20221,6 +20162,685 @@
       <c r="AM112" s="10" t="n"/>
       <c r="AN112" s="10" t="n"/>
       <c r="AO112" s="11" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>287622.79</v>
+      </c>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="18" t="n">
+        <v>1935769.63</v>
+      </c>
+      <c r="H113" s="18" t="n">
+        <v>241855.52</v>
+      </c>
+      <c r="I113" s="18" t="n">
+        <v>190635.03</v>
+      </c>
+      <c r="J113" s="18" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="K113" s="35" t="n">
+        <v>2368288.47</v>
+      </c>
+      <c r="L113" s="18" t="n">
+        <v>22971.1</v>
+      </c>
+      <c r="M113" s="18" t="n">
+        <v>188658.4</v>
+      </c>
+      <c r="N113" s="18" t="n">
+        <v>17158.17</v>
+      </c>
+      <c r="O113" s="18" t="n">
+        <v>13603.23</v>
+      </c>
+      <c r="P113" s="35" t="n">
+        <v>242390.9</v>
+      </c>
+      <c r="Q113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" s="9" t="n"/>
+      <c r="AB113" s="5" t="n"/>
+      <c r="AC113" s="10" t="n"/>
+      <c r="AD113" s="10" t="n"/>
+      <c r="AE113" s="11" t="n"/>
+      <c r="AF113" s="10" t="n"/>
+      <c r="AG113" s="10" t="n"/>
+      <c r="AH113" s="10" t="n"/>
+      <c r="AI113" s="10" t="n"/>
+      <c r="AJ113" s="11" t="n"/>
+      <c r="AK113" s="10" t="n"/>
+      <c r="AL113" s="10" t="n"/>
+      <c r="AM113" s="10" t="n"/>
+      <c r="AN113" s="10" t="n"/>
+      <c r="AO113" s="11" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="E114" s="18" t="n">
+        <v>836013.09</v>
+      </c>
+      <c r="F114" s="9" t="n"/>
+      <c r="G114" s="18" t="n">
+        <v>346221.39</v>
+      </c>
+      <c r="H114" s="18" t="n">
+        <v>127131.44</v>
+      </c>
+      <c r="I114" s="18" t="n">
+        <v>12405.36</v>
+      </c>
+      <c r="J114" s="18" t="n">
+        <v>432084.47</v>
+      </c>
+      <c r="K114" s="35" t="n">
+        <v>917842.66</v>
+      </c>
+      <c r="L114" s="18" t="n">
+        <v>113550.5</v>
+      </c>
+      <c r="M114" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="N114" s="18" t="n">
+        <v>504877.14</v>
+      </c>
+      <c r="O114" s="18" t="n">
+        <v>102500</v>
+      </c>
+      <c r="P114" s="35" t="n">
+        <v>735927.64</v>
+      </c>
+      <c r="Q114" s="18" t="n">
+        <v>743000</v>
+      </c>
+      <c r="R114" s="18" t="n">
+        <v>117500</v>
+      </c>
+      <c r="S114" s="18" t="n">
+        <v>261063.36</v>
+      </c>
+      <c r="T114" s="18" t="n">
+        <v>427399.64</v>
+      </c>
+      <c r="U114" s="35" t="n">
+        <v>1548963</v>
+      </c>
+      <c r="V114" s="18" t="n">
+        <v>52900</v>
+      </c>
+      <c r="W114" s="18" t="n">
+        <v>177100</v>
+      </c>
+      <c r="Y114" s="18" t="n">
+        <v>16250</v>
+      </c>
+      <c r="Z114" s="9" t="n"/>
+      <c r="AA114" s="18" t="n">
+        <v>153583</v>
+      </c>
+      <c r="AB114" s="19" t="n">
+        <v>29584</v>
+      </c>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="11" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="11" t="n"/>
+      <c r="AK114" s="10" t="n"/>
+      <c r="AL114" s="10" t="n"/>
+      <c r="AM114" s="10" t="n"/>
+      <c r="AN114" s="10" t="n"/>
+      <c r="AO114" s="11" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="n">
+        <v>23524.24</v>
+      </c>
+      <c r="F115" s="9" t="n"/>
+      <c r="G115" s="18" t="n">
+        <v>19001.42</v>
+      </c>
+      <c r="H115" s="18" t="n">
+        <v>26700.82</v>
+      </c>
+      <c r="I115" s="18" t="n">
+        <v>9748.52</v>
+      </c>
+      <c r="J115" s="18" t="n">
+        <v>24055.71</v>
+      </c>
+      <c r="K115" s="35" t="n">
+        <v>79506.47</v>
+      </c>
+      <c r="L115" s="18" t="n">
+        <v>18610.11</v>
+      </c>
+      <c r="M115" s="18" t="n">
+        <v>22363.11</v>
+      </c>
+      <c r="N115" s="18" t="n">
+        <v>18010.72</v>
+      </c>
+      <c r="O115" s="18" t="n">
+        <v>25169.71</v>
+      </c>
+      <c r="P115" s="35" t="n">
+        <v>84153.64999999999</v>
+      </c>
+      <c r="Q115" s="18" t="n">
+        <v>20373.78</v>
+      </c>
+      <c r="R115" s="18" t="n">
+        <v>20760.88</v>
+      </c>
+      <c r="S115" s="18" t="n">
+        <v>23131.57</v>
+      </c>
+      <c r="T115" s="18" t="n">
+        <v>29800.77</v>
+      </c>
+      <c r="U115" s="35" t="n">
+        <v>94067</v>
+      </c>
+      <c r="V115" s="18" t="n">
+        <v>24723</v>
+      </c>
+      <c r="W115" s="18" t="n">
+        <v>26626</v>
+      </c>
+      <c r="X115" s="18" t="n">
+        <v>27173</v>
+      </c>
+      <c r="Y115" s="18" t="n">
+        <v>30945</v>
+      </c>
+      <c r="Z115" s="35" t="n">
+        <v>109467</v>
+      </c>
+      <c r="AA115" s="18" t="n">
+        <v>25911</v>
+      </c>
+      <c r="AB115" s="19" t="n">
+        <v>28465</v>
+      </c>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="11" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="11" t="n"/>
+      <c r="AK115" s="10" t="n"/>
+      <c r="AL115" s="10" t="n"/>
+      <c r="AM115" s="10" t="n"/>
+      <c r="AN115" s="10" t="n"/>
+      <c r="AO115" s="11" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="9" t="n"/>
+      <c r="K116" s="9" t="n"/>
+      <c r="P116" s="9" t="n"/>
+      <c r="U116" s="9" t="n"/>
+      <c r="Z116" s="9" t="n"/>
+      <c r="AB116" s="5" t="n"/>
+      <c r="AC116" s="10" t="n"/>
+      <c r="AD116" s="10" t="n"/>
+      <c r="AE116" s="11" t="n"/>
+      <c r="AF116" s="10" t="n"/>
+      <c r="AG116" s="10" t="n"/>
+      <c r="AH116" s="10" t="n"/>
+      <c r="AI116" s="10" t="n"/>
+      <c r="AJ116" s="11" t="n"/>
+      <c r="AK116" s="10" t="n"/>
+      <c r="AL116" s="10" t="n"/>
+      <c r="AM116" s="10" t="n"/>
+      <c r="AN116" s="10" t="n"/>
+      <c r="AO116" s="11" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="n">
+        <v>103901.2</v>
+      </c>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="18" t="n">
+        <v>-320352.95</v>
+      </c>
+      <c r="H117" s="18" t="n">
+        <v>-490837.54</v>
+      </c>
+      <c r="I117" s="18" t="n">
+        <v>369611.48</v>
+      </c>
+      <c r="J117" s="18" t="n">
+        <v>-71187.38</v>
+      </c>
+      <c r="K117" s="35" t="n">
+        <v>-512766.39</v>
+      </c>
+      <c r="L117" s="18" t="n">
+        <v>196057.84</v>
+      </c>
+      <c r="M117" s="18" t="n">
+        <v>1132627.03</v>
+      </c>
+      <c r="N117" s="18" t="n">
+        <v>-454345.21</v>
+      </c>
+      <c r="O117" s="18" t="n">
+        <v>350009.73</v>
+      </c>
+      <c r="P117" s="35" t="n">
+        <v>1224349.39</v>
+      </c>
+      <c r="Q117" s="18" t="n">
+        <v>299912.81</v>
+      </c>
+      <c r="R117" s="18" t="n">
+        <v>-334324.58</v>
+      </c>
+      <c r="S117" s="18" t="n">
+        <v>-298168.3</v>
+      </c>
+      <c r="T117" s="18" t="n">
+        <v>610691.0699999999</v>
+      </c>
+      <c r="U117" s="35" t="n">
+        <v>278111</v>
+      </c>
+      <c r="V117" s="18" t="n">
+        <v>-288638</v>
+      </c>
+      <c r="W117" s="18" t="n">
+        <v>-335355</v>
+      </c>
+      <c r="X117" s="18" t="n">
+        <v>129896</v>
+      </c>
+      <c r="Y117" s="18" t="n">
+        <v>676796</v>
+      </c>
+      <c r="Z117" s="35" t="n">
+        <v>182699</v>
+      </c>
+      <c r="AA117" s="18" t="n">
+        <v>9533</v>
+      </c>
+      <c r="AB117" s="19" t="n">
+        <v>-548642</v>
+      </c>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="11" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="11" t="n"/>
+      <c r="AK117" s="10" t="n"/>
+      <c r="AL117" s="10" t="n"/>
+      <c r="AM117" s="10" t="n"/>
+      <c r="AN117" s="10" t="n"/>
+      <c r="AO117" s="11" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="n">
+        <v>103901.2</v>
+      </c>
+      <c r="F118" s="9" t="n"/>
+      <c r="G118" s="18" t="n">
+        <v>1588251.04</v>
+      </c>
+      <c r="H118" s="18" t="n">
+        <v>-490837.54</v>
+      </c>
+      <c r="I118" s="18" t="n">
+        <v>369611.48</v>
+      </c>
+      <c r="J118" s="18" t="n">
+        <v>-71187.38</v>
+      </c>
+      <c r="K118" s="35" t="n">
+        <v>1395837.6</v>
+      </c>
+      <c r="L118" s="18" t="n">
+        <v>1591895.43</v>
+      </c>
+      <c r="M118" s="18" t="n">
+        <v>1132627.04</v>
+      </c>
+      <c r="N118" s="18" t="n">
+        <v>-454345.21</v>
+      </c>
+      <c r="O118" s="18" t="n">
+        <v>350009.72</v>
+      </c>
+      <c r="P118" s="35" t="n">
+        <v>2620186.98</v>
+      </c>
+      <c r="Q118" s="18" t="n">
+        <v>2920099.79</v>
+      </c>
+      <c r="R118" s="18" t="n">
+        <v>-334324.57</v>
+      </c>
+      <c r="S118" s="18" t="n">
+        <v>-298168.31</v>
+      </c>
+      <c r="T118" s="18" t="n">
+        <v>610691.09</v>
+      </c>
+      <c r="U118" s="35" t="n">
+        <v>2898298</v>
+      </c>
+      <c r="V118" s="18" t="n">
+        <v>2609660</v>
+      </c>
+      <c r="W118" s="18" t="n">
+        <v>-335355</v>
+      </c>
+      <c r="X118" s="18" t="n">
+        <v>129896</v>
+      </c>
+      <c r="Y118" s="18" t="n">
+        <v>676796</v>
+      </c>
+      <c r="Z118" s="35" t="n">
+        <v>3080997</v>
+      </c>
+      <c r="AA118" s="18" t="n">
+        <v>3090530</v>
+      </c>
+      <c r="AB118" s="19" t="n">
+        <v>-548642</v>
+      </c>
+      <c r="AC118" s="10" t="n"/>
+      <c r="AD118" s="10" t="n"/>
+      <c r="AE118" s="11" t="n"/>
+      <c r="AF118" s="10" t="n"/>
+      <c r="AG118" s="10" t="n"/>
+      <c r="AH118" s="10" t="n"/>
+      <c r="AI118" s="10" t="n"/>
+      <c r="AJ118" s="11" t="n"/>
+      <c r="AK118" s="10" t="n"/>
+      <c r="AL118" s="10" t="n"/>
+      <c r="AM118" s="10" t="n"/>
+      <c r="AN118" s="10" t="n"/>
+      <c r="AO118" s="11" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="n"/>
+      <c r="G119" s="18" t="n">
+        <v>264.4</v>
+      </c>
+      <c r="H119" s="18" t="n">
+        <v>1398398.16</v>
+      </c>
+      <c r="I119" s="18" t="n">
+        <v>139746.7</v>
+      </c>
+      <c r="J119" s="18" t="n">
+        <v>130625.53</v>
+      </c>
+      <c r="K119" s="35" t="n">
+        <v>1669034.79</v>
+      </c>
+      <c r="L119" s="18" t="n">
+        <v>68903.58</v>
+      </c>
+      <c r="M119" s="18" t="n">
+        <v>104109.82</v>
+      </c>
+      <c r="N119" s="18" t="n">
+        <v>213919.53</v>
+      </c>
+      <c r="O119" s="18" t="n">
+        <v>3878.58</v>
+      </c>
+      <c r="P119" s="35" t="n">
+        <v>390811.51</v>
+      </c>
+      <c r="Q119" s="18" t="n">
+        <v>169156.77</v>
+      </c>
+      <c r="R119" s="18" t="n">
+        <v>3223.79</v>
+      </c>
+      <c r="S119" s="18" t="n">
+        <v>202808.55</v>
+      </c>
+      <c r="T119" s="18" t="n">
+        <v>90043.89</v>
+      </c>
+      <c r="U119" s="35" t="n">
+        <v>465233</v>
+      </c>
+      <c r="V119" s="18" t="n">
+        <v>397326</v>
+      </c>
+      <c r="X119" s="18" t="n">
+        <v>25737</v>
+      </c>
+      <c r="Y119" s="18" t="n">
+        <v>382368</v>
+      </c>
+      <c r="Z119" s="9" t="n"/>
+      <c r="AA119" s="18" t="n">
+        <v>6154</v>
+      </c>
+      <c r="AB119" s="19" t="n">
+        <v>26321</v>
+      </c>
+      <c r="AC119" s="10" t="n"/>
+      <c r="AD119" s="10" t="n"/>
+      <c r="AE119" s="11" t="n"/>
+      <c r="AF119" s="10" t="n"/>
+      <c r="AG119" s="10" t="n"/>
+      <c r="AH119" s="10" t="n"/>
+      <c r="AI119" s="10" t="n"/>
+      <c r="AJ119" s="11" t="n"/>
+      <c r="AK119" s="10" t="n"/>
+      <c r="AL119" s="10" t="n"/>
+      <c r="AM119" s="10" t="n"/>
+      <c r="AN119" s="10" t="n"/>
+      <c r="AO119" s="11" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>사채의감소</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="n"/>
+      <c r="I120" s="18" t="n">
+        <v>11104.95</v>
+      </c>
+      <c r="J120" s="18" t="n">
+        <v>7118.17</v>
+      </c>
+      <c r="K120" s="9" t="n"/>
+      <c r="P120" s="9" t="n"/>
+      <c r="U120" s="9" t="n"/>
+      <c r="Z120" s="9" t="n"/>
+      <c r="AB120" s="5" t="n"/>
+      <c r="AC120" s="10" t="n"/>
+      <c r="AD120" s="10" t="n"/>
+      <c r="AE120" s="11" t="n"/>
+      <c r="AF120" s="10" t="n"/>
+      <c r="AG120" s="10" t="n"/>
+      <c r="AH120" s="10" t="n"/>
+      <c r="AI120" s="10" t="n"/>
+      <c r="AJ120" s="11" t="n"/>
+      <c r="AK120" s="10" t="n"/>
+      <c r="AL120" s="10" t="n"/>
+      <c r="AM120" s="10" t="n"/>
+      <c r="AN120" s="10" t="n"/>
+      <c r="AO120" s="11" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="n"/>
+      <c r="I121" s="18" t="n">
+        <v>32052.63</v>
+      </c>
+      <c r="K121" s="9" t="n"/>
+      <c r="P121" s="9" t="n"/>
+      <c r="U121" s="9" t="n"/>
+      <c r="Z121" s="9" t="n"/>
+      <c r="AB121" s="5" t="n"/>
+      <c r="AC121" s="10" t="n"/>
+      <c r="AD121" s="10" t="n"/>
+      <c r="AE121" s="11" t="n"/>
+      <c r="AF121" s="10" t="n"/>
+      <c r="AG121" s="10" t="n"/>
+      <c r="AH121" s="10" t="n"/>
+      <c r="AI121" s="10" t="n"/>
+      <c r="AJ121" s="11" t="n"/>
+      <c r="AK121" s="10" t="n"/>
+      <c r="AL121" s="10" t="n"/>
+      <c r="AM121" s="10" t="n"/>
+      <c r="AN121" s="10" t="n"/>
+      <c r="AO121" s="11" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="n"/>
+      <c r="K122" s="9" t="n"/>
+      <c r="P122" s="9" t="n"/>
+      <c r="Q122" s="18" t="n">
+        <v>228125</v>
+      </c>
+      <c r="R122" s="18" t="n">
+        <v>259807.97</v>
+      </c>
+      <c r="S122" s="18" t="n">
+        <v>536197.23</v>
+      </c>
+      <c r="T122" s="18" t="n">
+        <v>38738.8</v>
+      </c>
+      <c r="U122" s="35" t="n">
+        <v>1062869</v>
+      </c>
+      <c r="V122" s="18" t="n">
+        <v>209464</v>
+      </c>
+      <c r="X122" s="18" t="n">
+        <v>291757</v>
+      </c>
+      <c r="Z122" s="9" t="n"/>
+      <c r="AA122" s="18" t="n">
+        <v>685152</v>
+      </c>
+      <c r="AB122" s="19" t="n">
+        <v>331908</v>
+      </c>
+      <c r="AC122" s="10" t="n"/>
+      <c r="AD122" s="10" t="n"/>
+      <c r="AE122" s="11" t="n"/>
+      <c r="AF122" s="10" t="n"/>
+      <c r="AG122" s="10" t="n"/>
+      <c r="AH122" s="10" t="n"/>
+      <c r="AI122" s="10" t="n"/>
+      <c r="AJ122" s="11" t="n"/>
+      <c r="AK122" s="10" t="n"/>
+      <c r="AL122" s="10" t="n"/>
+      <c r="AM122" s="10" t="n"/>
+      <c r="AN122" s="10" t="n"/>
+      <c r="AO122" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20481,7 +21101,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6376,7 +6376,7 @@
         <v>78645.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>81850</v>
+        <v>81700</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2200008014009355</v>
+        <v>0.2200008014009354</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.4000001388428971</v>
+        <v>0.4000001388428973</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02376345087880756</v>
+        <v>0.02376345087880409</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05178054189737089</v>
+        <v>0.05178054189736901</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>81900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>81400</v>
+        <v>80400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6194,7 +6194,7 @@
         <v>94400</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>84000</v>
+        <v>84300</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>57000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>80400</v>
+        <v>80200</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>78645.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>81700</v>
+        <v>81425</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9528,11 +9528,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>81400</v>
+        <v>80400</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 82,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 81,100원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45517,7 +45517,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>237.11</v>
+        <v>234.2</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>81900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>80400</v>
+        <v>76700</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>57000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>80200</v>
+        <v>75200</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>78645.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>81425</v>
+        <v>80380</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9528,11 +9528,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>80400</v>
+        <v>76700</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 81,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 81,500원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45517,7 +45517,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>234.2</v>
+        <v>223.42</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2200008014009354</v>
+        <v>0.2200008014009355</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.4000001388428973</v>
+        <v>0.4000001388428971</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02376345087880409</v>
+        <v>0.02376345087880756</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05178054189736901</v>
+        <v>0.05178054189737089</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 81,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 80,500원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.2200008014009355</v>
+        <v>0.2200008014009354</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.4000001388428971</v>
+        <v>0.4000001388428973</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.02376345087880756</v>
+        <v>0.02376345087880409</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.05178054189737089</v>
+        <v>0.05178054189736901</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
         <v>81900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>76700</v>
+        <v>71700</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>57000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>75200</v>
+        <v>71200</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>78645.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>80380</v>
+        <v>78933.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9528,7 +9528,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>76700</v>
+        <v>71700</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45517,7 +45517,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>223.42</v>
+        <v>208.86</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>81900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>71700</v>
+        <v>70300</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>57000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>71200</v>
+        <v>67300</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>78645.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>78933.3</v>
+        <v>77614.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9528,11 +9528,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>71700</v>
+        <v>70300</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 80,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 78,000원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45517,7 +45517,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>208.86</v>
+        <v>204.78</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>81900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>70300</v>
+        <v>69400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>78645.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>77614.3</v>
+        <v>76525</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9528,11 +9528,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>70300</v>
+        <v>69400</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 78,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 71,500원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45517,7 +45517,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>204.78</v>
+        <v>202.16</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>81900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>69400</v>
+        <v>66600</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>57000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>67300</v>
+        <v>61300</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>78645.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>76525</v>
+        <v>73100</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9528,11 +9528,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>69400</v>
+        <v>66600</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 71,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 63,300원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45517,7 +45517,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>202.16</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/034020_model.xlsx
+++ b/argus/kship/models/034020_model.xlsx
@@ -4264,7 +4264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5135,35 +5135,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5254,35 +5254,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5373,35 +5373,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5492,35 +5492,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5611,35 +5611,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5730,35 +5730,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5849,35 +5849,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5968,35 +5968,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6103,7 +6103,7 @@
         <v>81900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>66600</v>
+        <v>57400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6285,7 +6285,7 @@
         <v>57000</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>61300</v>
+        <v>57200</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6376,7 +6376,7 @@
         <v>78645.2</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>73100</v>
+        <v>69225</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9528,11 +9528,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>66600</v>
+        <v>57400</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 63,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 61,600원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -45517,7 +45517,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>194</v>
+        <v>167.2</v>
       </c>
     </row>
     <row r="32">
